--- a/docs/downloads/07/tbl_rente_exploitee_marovoay_tous.xlsx
+++ b/docs/downloads/07/tbl_rente_exploitee_marovoay_tous.xlsx
@@ -389,7 +389,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -410,7 +410,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -434,7 +434,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
